--- a/excel/data.xlsx
+++ b/excel/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\onkar\git\WebAutomation\WebAutomation\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{147BD26A-5B01-476E-998D-C3F5149F431E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A5603C-8229-42DF-80D3-C453744FDE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
